--- a/data/Input/AT 05.11 - 05.15.xlsx
+++ b/data/Input/AT 05.11 - 05.15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\eduar\Metricas\data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DF5698-E56F-475E-8294-C90036765554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD6001E-4640-45B1-8B2B-C9986577E3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,7 +109,7 @@
     <t>5000 - OPERATIONS</t>
   </si>
   <si>
-    <t>Week: 11/04/2026 - 15/08/2026</t>
+    <t>Week: 05/11/2026 - 05/15/2026</t>
   </si>
 </sst>
 </file>
@@ -696,23 +696,23 @@
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
-        <v>29.8</v>
-      </c>
-      <c r="D10">
-        <v>3.1</v>
-      </c>
-      <c r="E10">
-        <v>32.9</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
+      <c r="C10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G10">
         <v>37.5</v>
       </c>
-      <c r="H10">
-        <v>8.2249999999999996</v>
+      <c r="H10" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
